--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="503">
   <si>
     <t>Filename</t>
   </si>
@@ -808,712 +808,721 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9956,0.0006,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0004,0.0002,0.9992</t>
-  </si>
-  <si>
-    <t>0.9364,0.0010,0.0001,0.0387</t>
-  </si>
-  <si>
-    <t>0.0245,0.0017,0.0004,0.9907</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9892,0.0019,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.0007,0.0005,0.9984</t>
+  </si>
+  <si>
+    <t>0.9959,0.0001,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.0054,0.0002,0.0000,0.9987</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
+    <t>0.9995,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9843,0.0004,0.0098,0.0000</t>
+  </si>
+  <si>
+    <t>0.0155,0.0023,0.9785,0.0005</t>
+  </si>
+  <si>
+    <t>0.1427,0.0019,0.8897,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0010,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0001,0.0050,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0059,0.9948,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9533,0.0005,0.0293,0.0004</t>
+  </si>
+  <si>
+    <t>0.0545,0.0020,0.9290,0.0008</t>
+  </si>
+  <si>
+    <t>0.0065,0.0003,0.9950,0.0001</t>
+  </si>
+  <si>
+    <t>0.0373,0.0011,0.9452,0.0016</t>
+  </si>
+  <si>
+    <t>0.1995,0.0000,0.9113,0.0000</t>
+  </si>
+  <si>
+    <t>0.8476,0.0002,0.1848,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0014</t>
+  </si>
+  <si>
+    <t>0.0955,0.9207,0.0025,0.0005</t>
+  </si>
+  <si>
+    <t>0.9589,0.0148,0.0122,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0026,0.9997,0.0050</t>
+  </si>
+  <si>
+    <t>0.0008,0.9990,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9860,0.0003,0.0163,0.0001</t>
+  </si>
+  <si>
+    <t>0.2456,0.0004,0.8346,0.0007</t>
+  </si>
+  <si>
+    <t>0.2960,0.7192,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9985,0.0106,0.0000</t>
+  </si>
+  <si>
+    <t>0.0110,0.8181,0.1170,0.0014</t>
+  </si>
+  <si>
+    <t>0.0338,0.0003,0.9307,0.0017</t>
+  </si>
+  <si>
+    <t>0.0094,0.0160,0.9717,0.0016</t>
+  </si>
+  <si>
+    <t>0.0072,0.0000,0.9879,0.0016</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0015,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.3033,0.0009,0.9063</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0371,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.3925,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.1223,0.9938,0.0007</t>
+  </si>
+  <si>
+    <t>0.9669,0.0414,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0023,0.9993,0.0058</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0009,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.6649,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0285,0.9947,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.0011,0.9921,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.9951,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.2556,0.0003,0.8453,0.0001</t>
+  </si>
+  <si>
+    <t>0.3340,0.0040,0.6191,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.0004,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9944,0.4961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.7282,0.9847,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0120,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0017,0.9991</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.0000,0.0000,0.9991</t>
+  </si>
+  <si>
+    <t>0.0051,0.0015,0.0007,0.9963</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0114,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0331,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0727,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9927,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0238,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9910,0.0135,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9940,0.0052,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0060,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0007</t>
+  </si>
+  <si>
+    <t>0.0039,0.0012,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.7700,0.0004,0.2473,0.0008</t>
+  </si>
+  <si>
+    <t>0.0267,0.0001,0.9880,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9979,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.5112,0.6480,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.4227,0.2042,0.0633,0.0006</t>
+  </si>
+  <si>
+    <t>0.9938,0.0000,0.0074,0.0000</t>
+  </si>
+  <si>
+    <t>0.0364,0.6083,0.0777,0.0162</t>
+  </si>
+  <si>
+    <t>0.3146,0.0041,0.5345,0.0019</t>
+  </si>
+  <si>
+    <t>0.0006,0.0322,0.0009,0.9961</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9875,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.5991,0.2868,0.0186,0.0001</t>
+  </si>
+  <si>
+    <t>0.4090,0.6460,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0038,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0009,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.7921,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.5742,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0018,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.0018,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.2064,0.0005,0.7865,0.0005</t>
+  </si>
+  <si>
+    <t>0.1181,0.0001,0.9042,0.0003</t>
+  </si>
+  <si>
+    <t>0.9330,0.0001,0.0816,0.0001</t>
+  </si>
+  <si>
+    <t>0.0558,0.0002,0.0002,0.9803</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9320,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.9941,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9799,0.0001,0.0063,0.0050</t>
+  </si>
+  <si>
+    <t>0.0005,0.0078,0.9960,0.0154</t>
+  </si>
+  <si>
+    <t>0.8188,0.0000,0.0581,0.0081</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.4537,0.7280,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0017,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0938,0.8205,0.0221,0.0001</t>
+  </si>
+  <si>
+    <t>0.9586,0.0104,0.0162,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0010,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0000,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9292,0.0210,0.0000,0.0022</t>
+  </si>
+  <si>
+    <t>0.3486,0.6582,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9207,0.1239,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9562,0.0129,0.0242,0.0016</t>
+  </si>
+  <si>
+    <t>0.9988,0.0022,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9916,0.0036,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9475,0.0648,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0023,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9863,0.0080,0.0050,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0056,0.9974,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0048,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.0045,0.9962,0.0010</t>
+  </si>
+  <si>
+    <t>0.0647,0.0009,0.9439,0.0001</t>
+  </si>
+  <si>
+    <t>0.0330,0.0025,0.9600,0.0001</t>
+  </si>
+  <si>
+    <t>0.1948,0.0057,0.7381,0.0002</t>
+  </si>
+  <si>
+    <t>0.0169,0.3164,0.7072,0.0001</t>
+  </si>
+  <si>
+    <t>0.0501,0.0002,0.9658,0.0000</t>
+  </si>
+  <si>
+    <t>0.9692,0.0003,0.0247,0.0001</t>
+  </si>
+  <si>
+    <t>0.0333,0.0021,0.9657,0.0002</t>
+  </si>
+  <si>
+    <t>0.0449,0.9691,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0177,0.9864,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9509,0.0935,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4196,0.7427,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1041,0.9206,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.8535,0.1375,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0000,0.0028,0.0000</t>
+  </si>
+  <si>
+    <t>0.9611,0.0020,0.0075,0.0022</t>
+  </si>
+  <si>
+    <t>0.5915,0.0011,0.4204,0.0003</t>
+  </si>
+  <si>
+    <t>0.0114,0.0057,0.9666,0.0114</t>
+  </si>
+  <si>
+    <t>0.0049,0.0011,0.9915,0.0005</t>
+  </si>
+  <si>
+    <t>0.0078,0.0263,0.9036,0.0122</t>
+  </si>
+  <si>
+    <t>0.0288,0.0091,0.9530,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0045,0.9954,0.0005</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0013,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9899,0.0076,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9909,0.0053,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9974,0.0024,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.0332,0.0103,0.9391,0.0004</t>
+  </si>
+  <si>
+    <t>0.9928,0.0007,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.0488,0.0000,0.9733,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0038,0.9933,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.3179,0.9929,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0014,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.1673,0.0036,0.7096,0.0046</t>
+  </si>
+  <si>
+    <t>0.9955,0.0000,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9820,0.0141,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0002</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9542,0.0009,0.0365,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0012,0.9925,0.0001</t>
-  </si>
-  <si>
-    <t>0.7612,0.0016,0.2987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.2866,0.0004,0.7810,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0113,0.9911,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9694,0.0005,0.0229,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.0015,0.9872,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0006,0.9953,0.0002</t>
-  </si>
-  <si>
-    <t>0.0647,0.0000,0.9701,0.0000</t>
-  </si>
-  <si>
-    <t>0.4402,0.0003,0.6434,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9992,0.0004</t>
-  </si>
-  <si>
-    <t>0.4747,0.6400,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9332,0.0172,0.0218,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0018,0.9998,0.0026</t>
-  </si>
-  <si>
-    <t>0.0141,0.9739,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0001,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.1258,0.8849,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.0343,0.7904,0.0618,0.0008</t>
-  </si>
-  <si>
-    <t>0.1414,0.0002,0.7327,0.0037</t>
-  </si>
-  <si>
-    <t>0.0011,0.0128,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.0084,0.0004,0.9872,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.0121,0.9949,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9990,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.9753,0.0011,0.6124</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0516,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0236,0.9916,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0000,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9994,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.3049,0.9967,0.0004</t>
-  </si>
-  <si>
-    <t>0.9940,0.0040,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0023,0.9993,0.0024</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9936,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0061,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0031,0.9929,0.0021</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9337,0.0001,0.1509,0.0000</t>
-  </si>
-  <si>
-    <t>0.9770,0.0033,0.0079,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0009,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9973,0.1961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8123,0.9833,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.9399,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0243,0.9985</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0007,0.0005,0.0007,0.9990</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.2444,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.0968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.2557,0.9893,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9926,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.1748,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0024,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0024,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0034,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0013</t>
-  </si>
-  <si>
-    <t>0.0036,0.0006,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.3459,0.0006,0.5459,0.0090</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.9943,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9045,0.1685,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8820,0.0145,0.0262,0.0021</t>
-  </si>
-  <si>
-    <t>0.9412,0.0001,0.1018,0.0000</t>
-  </si>
-  <si>
-    <t>0.1099,0.8500,0.0034,0.0108</t>
-  </si>
-  <si>
-    <t>0.3993,0.1123,0.0210,0.0580</t>
-  </si>
-  <si>
-    <t>0.0010,0.0021,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.7764,0.1387,0.0169,0.0001</t>
-  </si>
-  <si>
-    <t>0.4861,0.5589,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0016,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9969,0.0002,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.1315,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.2453,0.9925,0.0000</t>
-  </si>
-  <si>
-    <t>0.0069,0.0058,0.9820,0.0002</t>
-  </si>
-  <si>
-    <t>0.0123,0.0016,0.9859,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2492,0.0005,0.7997,0.0001</t>
-  </si>
-  <si>
-    <t>0.2308,0.0001,0.8265,0.0003</t>
-  </si>
-  <si>
-    <t>0.9616,0.0003,0.0265,0.0002</t>
-  </si>
-  <si>
-    <t>0.2141,0.0001,0.0001,0.9223</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
+    <t>0.9981,0.0026,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0057,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0288,0.0050,0.9439,0.0003</t>
+  </si>
+  <si>
+    <t>0.1359,0.0003,0.8944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0018,0.8523,0.3017</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0001,0.9950,0.0010</t>
+  </si>
+  <si>
+    <t>0.9776,0.0000,0.0060,0.0024</t>
+  </si>
+  <si>
+    <t>0.0000,0.0197,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0110,0.0000,0.0007,0.9938</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.0000,0.9988,0.9817,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9977,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0060,0.9911,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9525,0.0003,0.0028,0.0415</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9994,0.0022</t>
-  </si>
-  <si>
-    <t>0.9823,0.0000,0.0178,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.1829,0.8283,0.0021,0.0015</t>
-  </si>
-  <si>
-    <t>0.9957,0.0027,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.1084,0.3138,0.2580,0.0001</t>
-  </si>
-  <si>
-    <t>0.9299,0.0111,0.0321,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0012,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0006,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9842,0.0119,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.7862,0.2254,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.8928,0.1534,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8034,0.0143,0.1526,0.0035</t>
-  </si>
-  <si>
-    <t>0.9985,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9978,0.0008,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.8564,0.1750,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0014,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0270,0.9978,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0172,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9997,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.1619,0.0008,0.8694,0.0006</t>
-  </si>
-  <si>
-    <t>0.0149,0.0062,0.9638,0.0004</t>
-  </si>
-  <si>
-    <t>0.0873,0.0119,0.8531,0.0003</t>
-  </si>
-  <si>
-    <t>0.0091,0.1567,0.8584,0.0001</t>
-  </si>
-  <si>
-    <t>0.5475,0.0035,0.4390,0.0000</t>
-  </si>
-  <si>
-    <t>0.0979,0.0006,0.9178,0.0002</t>
-  </si>
-  <si>
-    <t>0.0180,0.0016,0.9755,0.0008</t>
-  </si>
-  <si>
-    <t>0.0429,0.9716,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.9976,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9895,0.0140,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.5552,0.5560,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0126,0.9855,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.7786,0.0928,0.0105,0.0018</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.0024,0.9886,0.0014</t>
-  </si>
-  <si>
-    <t>0.2459,0.0161,0.5368,0.0056</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9995,0.0008</t>
-  </si>
-  <si>
-    <t>0.0020,0.0081,0.9846,0.0033</t>
-  </si>
-  <si>
-    <t>0.0399,0.0114,0.9482,0.0003</t>
-  </si>
-  <si>
-    <t>0.0151,0.0023,0.9751,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.9138,0.2650,0.0013</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0024,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9934,0.0061,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.0180,0.0058,0.9643,0.0008</t>
-  </si>
-  <si>
-    <t>0.9687,0.0019,0.0093,0.0055</t>
-  </si>
-  <si>
-    <t>0.3239,0.0000,0.8436,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0031,0.9957,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0074,0.9961,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0788,0.0003,0.9384,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0043,0.9967,0.0012</t>
-  </si>
-  <si>
-    <t>0.8826,0.0000,0.1504,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0000,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0000,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0018,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0025,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0042,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0011,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0028,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0017,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0047,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0391,0.0202,0.8983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0125,0.0001,0.9894,0.0001</t>
-  </si>
-  <si>
-    <t>0.0242,0.0009,0.9540,0.0042</t>
-  </si>
-  <si>
-    <t>0.0030,0.0012,0.9928,0.0003</t>
-  </si>
-  <si>
-    <t>0.0698,0.0028,0.8796,0.0020</t>
-  </si>
-  <si>
-    <t>0.9875,0.0001,0.0008,0.0033</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.0002,0.9993</t>
-  </si>
-  <si>
-    <t>0.0178,0.0002,0.0096,0.9778</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0001,0.0001</t>
+    <t>0.9979,0.0000,0.0000,0.0003</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1908,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1913,7 +1922,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1927,7 +1936,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1941,7 +1950,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1955,7 +1964,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1969,7 +1978,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1983,7 +1992,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1997,7 +2006,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2011,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2025,7 +2034,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2039,7 +2048,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2053,7 +2062,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2067,7 +2076,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2081,7 +2090,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2092,10 +2101,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2109,7 +2118,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2120,10 +2129,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2137,7 +2146,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2151,7 +2160,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2165,7 +2174,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2179,7 +2188,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2193,7 +2202,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2207,7 +2216,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2221,7 +2230,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2235,7 +2244,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2249,7 +2258,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2263,7 +2272,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2274,10 +2283,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2291,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2305,7 +2314,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2319,7 +2328,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2333,7 +2342,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2347,7 +2356,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2361,7 +2370,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2372,10 +2381,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2389,7 +2398,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2403,7 +2412,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2417,7 +2426,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2431,7 +2440,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2445,7 +2454,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2459,7 +2468,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2473,7 +2482,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2487,7 +2496,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2501,7 +2510,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2512,10 +2521,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2529,7 +2538,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2543,7 +2552,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2557,7 +2566,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2571,7 +2580,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2585,7 +2594,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2599,7 +2608,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2613,7 +2622,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2627,7 +2636,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2641,7 +2650,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2655,7 +2664,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2669,7 +2678,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2683,7 +2692,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2697,7 +2706,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2711,7 +2720,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2725,7 +2734,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2739,7 +2748,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2753,7 +2762,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2767,7 +2776,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2781,7 +2790,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2795,7 +2804,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2809,7 +2818,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2823,7 +2832,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2837,7 +2846,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2848,10 +2857,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2862,10 +2871,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2879,7 +2888,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2893,7 +2902,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2907,7 +2916,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2921,7 +2930,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2932,10 +2941,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2949,7 +2958,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2963,7 +2972,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2977,7 +2986,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2991,7 +3000,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3005,7 +3014,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3019,7 +3028,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3033,7 +3042,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3047,7 +3056,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3061,7 +3070,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3075,7 +3084,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3089,7 +3098,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3103,7 +3112,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3117,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3131,7 +3140,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3145,7 +3154,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3159,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3173,7 +3182,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3187,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3201,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3215,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3243,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3257,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3271,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3285,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3299,7 +3308,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>354</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3313,7 +3322,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>319</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3327,7 +3336,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>359</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3341,7 +3350,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3355,7 +3364,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3366,10 +3375,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3383,7 +3392,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3397,7 +3406,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3411,7 +3420,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>283</v>
+        <v>365</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3425,7 +3434,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3439,7 +3448,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3453,7 +3462,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3467,7 +3476,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3478,10 +3487,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3492,10 +3501,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3509,7 +3518,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3523,7 +3532,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3534,10 +3543,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3551,7 +3560,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3565,7 +3574,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3579,7 +3588,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3593,7 +3602,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3607,7 +3616,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3621,7 +3630,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3635,7 +3644,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3649,7 +3658,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3663,7 +3672,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3677,7 +3686,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3691,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3705,7 +3714,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3719,7 +3728,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3733,7 +3742,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3747,7 +3756,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3761,7 +3770,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3772,10 +3781,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3786,10 +3795,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3803,7 +3812,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3817,7 +3826,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3831,7 +3840,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3845,7 +3854,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3859,7 +3868,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3873,7 +3882,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3887,7 +3896,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3901,7 +3910,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>392</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3915,7 +3924,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>393</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3929,7 +3938,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3943,7 +3952,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3957,7 +3966,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3971,7 +3980,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3985,7 +3994,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3999,7 +4008,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4013,7 +4022,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4027,7 +4036,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4041,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4055,7 +4064,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4069,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4083,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4097,7 +4106,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4111,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4125,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4136,10 +4145,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4153,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4167,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4181,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4195,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4209,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4223,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4237,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4251,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4265,7 +4274,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4279,7 +4288,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4293,7 +4302,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4304,10 +4313,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4321,7 +4330,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4335,7 +4344,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4349,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4363,7 +4372,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4377,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4391,7 +4400,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4405,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4419,7 +4428,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4433,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4447,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4461,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4475,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4489,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4503,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4517,7 +4526,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4531,7 +4540,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4545,7 +4554,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4559,7 +4568,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4573,7 +4582,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4587,7 +4596,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4598,10 +4607,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4612,10 +4621,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4629,7 +4638,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4643,7 +4652,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4657,7 +4666,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4671,7 +4680,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4685,7 +4694,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4699,7 +4708,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4713,7 +4722,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4727,7 +4736,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4741,7 +4750,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4752,10 +4761,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4769,7 +4778,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4783,7 +4792,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4797,7 +4806,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4811,7 +4820,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4825,7 +4834,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4836,10 +4845,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4853,7 +4862,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4867,7 +4876,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4881,7 +4890,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4895,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4909,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4923,7 +4932,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4937,7 +4946,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4951,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4965,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4979,7 +4988,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4993,7 +5002,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5007,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5021,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5035,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5049,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5063,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5077,7 +5086,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5091,7 +5100,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>476</v>
+        <v>435</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5105,7 +5114,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5116,10 +5125,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5133,7 +5142,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5147,7 +5156,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5161,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5175,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5189,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>484</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5203,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5217,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5231,7 +5240,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5245,7 +5254,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5259,7 +5268,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>487</v>
+        <v>353</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5273,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5287,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5301,7 +5310,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5315,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5329,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5343,7 +5352,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5357,7 +5366,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5371,7 +5380,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5385,7 +5394,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5399,7 +5408,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5413,7 +5422,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5427,7 +5436,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>392</v>
+        <v>500</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5441,7 +5450,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>392</v>
+        <v>501</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5455,7 +5464,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
